--- a/branches/dev/StructureDefinition-mii-pr-mtb-diagnose-primaertumor.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-mtb-diagnose-primaertumor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T04:08:55+00:00</t>
+    <t>2026-09-15T04:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
